--- a/data/Excel/GuLiStrikeSecondaryWeapons.xlsx
+++ b/data/Excel/GuLiStrikeSecondaryWeapons.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
   <si>
     <t>id</t>
   </si>
@@ -566,6 +566,24 @@
   </si>
   <si>
     <t>所有AOE配置统一维护在 GuLiStrikeSpellFields.xlsx / Fields。此处填数字id；空白或0表示不产生法术场。导出时自动解析为UE行名引用。</t>
+  </si>
+  <si>
+    <t>扫荡者车身视觉瞄准点</t>
+  </si>
+  <si>
+    <t>扫荡者手工模型机枪口；保留 BasicAttack 0</t>
+  </si>
+  <si>
+    <t>战争机器车身视觉瞄准点</t>
+  </si>
+  <si>
+    <t>战争机器左侧炮口；保留原攻击数量</t>
+  </si>
+  <si>
+    <t>战争机器左背舱出口；前上方 45 度</t>
+  </si>
+  <si>
+    <t>战争机器右背舱出口；前上方 45 度</t>
   </si>
 </sst>
 </file>
@@ -1590,7 +1608,7 @@
         <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>182</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1628,7 +1646,7 @@
         <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>183</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1646,13 +1664,13 @@
         <v>62</v>
       </c>
       <c r="I5">
-        <v>-480</v>
+        <v>757.2613716125488</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>935</v>
+        <v>588.1241798400879</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -1666,7 +1684,7 @@
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>184</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -1687,7 +1705,7 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>495</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <v>1600</v>
@@ -1704,7 +1722,7 @@
         <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>185</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -1722,13 +1740,13 @@
         <v>62</v>
       </c>
       <c r="I7">
-        <v>1490</v>
+        <v>1769.8602676391602</v>
       </c>
       <c r="J7">
-        <v>466</v>
+        <v>1461.23685836792</v>
       </c>
       <c r="K7">
-        <v>1810</v>
+        <v>1580.907154083252</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
@@ -1742,7 +1760,7 @@
         <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>186</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -1760,13 +1778,13 @@
         <v>69</v>
       </c>
       <c r="I8">
-        <v>-260</v>
+        <v>-729.1603565216064</v>
       </c>
       <c r="J8">
-        <v>1257</v>
+        <v>932.1683883666992</v>
       </c>
       <c r="K8">
-        <v>2440</v>
+        <v>3122.332191467285</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
@@ -1780,7 +1798,7 @@
         <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>187</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -1798,13 +1816,13 @@
         <v>72</v>
       </c>
       <c r="I9">
-        <v>-260</v>
+        <v>-729.1603565216064</v>
       </c>
       <c r="J9">
-        <v>-326</v>
+        <v>-932.1683883666992</v>
       </c>
       <c r="K9">
-        <v>2440</v>
+        <v>3122.332191467285</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>

--- a/data/Excel/GuLiStrikeSecondaryWeapons.xlsx
+++ b/data/Excel/GuLiStrikeSecondaryWeapons.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
   <si>
     <t>id</t>
   </si>
@@ -584,6 +584,45 @@
   </si>
   <si>
     <t>战争机器右背舱出口；前上方 45 度</t>
+  </si>
+  <si>
+    <t>TriggerMode</t>
+  </si>
+  <si>
+    <t>Automatic</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>主动Q导弹；技能CD6秒、普攻射程x0.8；保留本槽伤害升级与挂点，自动攻速列不参与Q冷却</t>
+  </si>
+  <si>
+    <t>战争机器Q主动导弹；定点弹道，爆炸由独立法术场结算</t>
+  </si>
+  <si>
+    <t>ProjectileSweepRadiusCentimeters</t>
+  </si>
+  <si>
+    <t>地面机枪直线飞行弹丸；碰撞扣血，弹道参数见UnitSkills</t>
+  </si>
+  <si>
+    <t>GroundMachineGun</t>
+  </si>
+  <si>
+    <t>地面兵种武器槽、伤害、每秒发数、开火射程；机枪弹速(cm/s)、寿命(s)、碰撞半径(cm)独立配置，兵种ID对应Commander/Soldiers。</t>
+  </si>
+  <si>
+    <t>飞行弹丸</t>
+  </si>
+  <si>
+    <t>正式Strafe为12000cm/s、5秒、碰撞半径15cm；服务端30Hz连续扫掠、地面存活状态5Hz同步，开火射程不截短弹丸寿命；僚机对空沿用自身弹丸参数；StrafeTest保留即时命中。</t>
+  </si>
+  <si>
+    <t>正式Strafe为12000cm/s、5秒、碰撞半径15cm；服务端地面弹丸5Hz连续扫掠、存活状态5Hz同步，开火射程不截短弹丸寿命；僚机对空沿用30Hz及自身弹丸参数；StrafeTest保留即时命中。</t>
+  </si>
+  <si>
+    <t>主动Q导弹；技能CD6秒、普攻射程x1.6；保留本槽伤害升级与挂点，自动攻速列不参与Q冷却</t>
   </si>
 </sst>
 </file>
@@ -941,7 +980,7 @@
         <v>138</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>139</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" ht="42" customHeight="true">
@@ -994,10 +1033,10 @@
     </row>
     <row r="9" ht="34" customHeight="true">
       <c r="A9" s="3" t="s">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>153</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="true">
@@ -1132,7 +1171,7 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>194</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
@@ -1141,7 +1180,7 @@
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>195</v>
       </c>
       <c r="G4" t="s">
         <v>16</v>
@@ -1184,7 +1223,7 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>192</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -1247,6 +1286,18 @@
       <c r="J1" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="K1" t="s">
+        <v>188</v>
+      </c>
+      <c r="L1" t="s">
+        <v>85</v>
+      </c>
+      <c r="M1" t="s">
+        <v>86</v>
+      </c>
+      <c r="N1" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
@@ -1279,6 +1330,18 @@
       <c r="J2" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="K2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
@@ -1311,6 +1374,18 @@
       <c r="J3" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="K3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -1338,10 +1413,22 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>10000</v>
+        <v>2000</v>
+      </c>
+      <c r="K4" t="s">
+        <v>189</v>
+      </c>
+      <c r="L4">
+        <v>2400</v>
+      </c>
+      <c r="M4">
+        <v>5</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -1370,10 +1457,22 @@
         <v>7.5</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>15000</v>
+        <v>3000</v>
+      </c>
+      <c r="K5" t="s">
+        <v>189</v>
+      </c>
+      <c r="L5">
+        <v>2400</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -1405,7 +1504,10 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>12000</v>
+        <v>2400</v>
+      </c>
+      <c r="K6" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1539,10 @@
         <v>2</v>
       </c>
       <c r="J7">
-        <v>18000</v>
+        <v>3600</v>
+      </c>
+      <c r="K7" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="8">
@@ -1448,7 +1553,7 @@
         <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>200</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -1469,7 +1574,10 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="J8">
-        <v>15000</v>
+        <v>3000</v>
+      </c>
+      <c r="K8" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -2145,13 +2253,13 @@
         <v>0.2</v>
       </c>
       <c r="I4">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="J4">
         <v>20</v>
       </c>
       <c r="K4">
-        <v>9000</v>
+        <v>1800</v>
       </c>
       <c r="L4">
         <v>1.5</v>
@@ -2160,16 +2268,16 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>12000</v>
+        <v>2400</v>
       </c>
       <c r="O4">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="P4">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="Q4">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="R4">
         <v>5</v>
@@ -2178,16 +2286,16 @@
         <v>3</v>
       </c>
       <c r="T4">
-        <v>80000</v>
+        <v>16000</v>
       </c>
       <c r="U4">
         <v>1.875</v>
       </c>
       <c r="V4">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>1200</v>
+        <v>240</v>
       </c>
       <c r="X4">
         <v>0</v>
@@ -2237,13 +2345,13 @@
         <v>8</v>
       </c>
       <c r="I5">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="J5">
         <v>20</v>
       </c>
       <c r="K5">
-        <v>9000</v>
+        <v>1800</v>
       </c>
       <c r="L5">
         <v>1.5</v>
@@ -2252,16 +2360,16 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>12000</v>
+        <v>2400</v>
       </c>
       <c r="O5">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="P5">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="Q5">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="R5">
         <v>5</v>
@@ -2270,16 +2378,16 @@
         <v>3</v>
       </c>
       <c r="T5">
-        <v>6000</v>
+        <v>1200</v>
       </c>
       <c r="U5">
         <v>8</v>
       </c>
       <c r="V5">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>1200</v>
+        <v>240</v>
       </c>
       <c r="X5">
         <v>0</v>
@@ -2329,7 +2437,7 @@
         <v>2</v>
       </c>
       <c r="I6">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="J6">
         <v>20</v>
@@ -2362,13 +2470,13 @@
         <v>0</v>
       </c>
       <c r="T6">
-        <v>120000</v>
+        <v>24000</v>
       </c>
       <c r="U6">
         <v>1.5</v>
       </c>
       <c r="V6">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>0</v>
@@ -2421,7 +2529,7 @@
         <v>8</v>
       </c>
       <c r="I7">
-        <v>250000</v>
+        <v>50000</v>
       </c>
       <c r="J7">
         <v>8</v>
@@ -2454,13 +2562,13 @@
         <v>0</v>
       </c>
       <c r="T7">
-        <v>45000</v>
+        <v>9000</v>
       </c>
       <c r="U7">
         <v>8</v>
       </c>
       <c r="V7">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="W7">
         <v>0</v>
@@ -2581,10 +2689,10 @@
         <v>104</v>
       </c>
       <c r="D4">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="E4">
-        <v>180000</v>
+        <v>36000</v>
       </c>
       <c r="F4">
         <v>0.8</v>
@@ -2772,28 +2880,28 @@
         <v>162</v>
       </c>
       <c r="E4">
-        <v>6000</v>
+        <v>1200</v>
       </c>
       <c r="F4">
         <v>0.25</v>
       </c>
       <c r="G4">
-        <v>600</v>
+        <v>120</v>
       </c>
       <c r="H4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="I4">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="J4">
-        <v>1600</v>
+        <v>320</v>
       </c>
       <c r="K4">
         <v>240</v>
       </c>
       <c r="L4">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>8</v>

--- a/data/Excel/GuLiStrikeSecondaryWeapons.xlsx
+++ b/data/Excel/GuLiStrikeSecondaryWeapons.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="217">
   <si>
     <t>id</t>
   </si>
@@ -623,6 +623,54 @@
   </si>
   <si>
     <t>主动Q导弹；技能CD6秒、普攻射程x1.6；保留本槽伤害升级与挂点，自动攻速列不参与Q冷却</t>
+  </si>
+  <si>
+    <t>WM01_BasicAttack_Muzzle_1</t>
+  </si>
+  <si>
+    <t>战争机器右侧双枪管；成功发射后交替</t>
+  </si>
+  <si>
+    <t>FX_Muzzle_Basic_02</t>
+  </si>
+  <si>
+    <t>重防号Q主动导弹；定点弹道，爆炸由独立法术场结算</t>
+  </si>
+  <si>
+    <t>重防号车身视觉瞄准点</t>
+  </si>
+  <si>
+    <t>重防号左侧炮口；保留原攻击数量</t>
+  </si>
+  <si>
+    <t>重防号左背舱出口；前上方 45 度</t>
+  </si>
+  <si>
+    <t>重防号右背舱出口；前上方 45 度</t>
+  </si>
+  <si>
+    <t>重防号右侧双枪管；成功发射后交替</t>
+  </si>
+  <si>
+    <t>VerticalCurveCentimeters</t>
+  </si>
+  <si>
+    <t>LongitudinalCurveCentimeters</t>
+  </si>
+  <si>
+    <t>SmokeInitialWidthCentimeters</t>
+  </si>
+  <si>
+    <t>SmokeMaximumWidthCentimeters</t>
+  </si>
+  <si>
+    <t>FlameWidthCentimeters</t>
+  </si>
+  <si>
+    <t>FlameLengthCentimeters</t>
+  </si>
+  <si>
+    <t>主动Q导弹；射程与冷却取SecondaryUnitSkills/Skills；保留本槽伤害升级与挂点，自动攻速列不参与Q冷却</t>
   </si>
 </sst>
 </file>
@@ -1223,7 +1271,7 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -1553,7 +1601,7 @@
         <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -1792,7 +1840,7 @@
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -1816,7 +1864,7 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1600</v>
+        <v>2354.9516318</v>
       </c>
       <c r="L6" t="b">
         <v>1</v>
@@ -1830,7 +1878,7 @@
         <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -1854,7 +1902,7 @@
         <v>1461.23685836792</v>
       </c>
       <c r="K7">
-        <v>1580.907154083252</v>
+        <v>2335.8587859</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
@@ -1868,7 +1916,7 @@
         <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -1892,7 +1940,7 @@
         <v>932.1683883666992</v>
       </c>
       <c r="K8">
-        <v>3122.332191467285</v>
+        <v>3877.28382</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
@@ -1906,7 +1954,7 @@
         <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -1930,9 +1978,47 @@
         <v>-932.1683883666992</v>
       </c>
       <c r="K9">
-        <v>3122.332191467285</v>
+        <v>3877.28382</v>
       </c>
       <c r="L9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>201</v>
+      </c>
+      <c r="C10" t="s">
+        <v>209</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>203</v>
+      </c>
+      <c r="I10">
+        <v>1769.8602676</v>
+      </c>
+      <c r="J10">
+        <v>-1468.7631416</v>
+      </c>
+      <c r="K10">
+        <v>2335.8587859</v>
+      </c>
+      <c r="L10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2765,6 +2851,24 @@
       <c r="P1" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="Q1" t="s">
+        <v>210</v>
+      </c>
+      <c r="R1" t="s">
+        <v>211</v>
+      </c>
+      <c r="S1" t="s">
+        <v>212</v>
+      </c>
+      <c r="T1" t="s">
+        <v>213</v>
+      </c>
+      <c r="U1" t="s">
+        <v>214</v>
+      </c>
+      <c r="V1" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
@@ -2815,6 +2919,24 @@
       <c r="P2" s="5" t="s">
         <v>9</v>
       </c>
+      <c r="Q2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U2" t="s">
+        <v>35</v>
+      </c>
+      <c r="V2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
@@ -2865,6 +2987,24 @@
       <c r="P3" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="Q3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S3" t="s">
+        <v>11</v>
+      </c>
+      <c r="T3" t="s">
+        <v>11</v>
+      </c>
+      <c r="U3" t="s">
+        <v>11</v>
+      </c>
+      <c r="V3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -2880,22 +3020,22 @@
         <v>162</v>
       </c>
       <c r="E4">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="F4">
         <v>0.25</v>
       </c>
       <c r="G4">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H4">
-        <v>200</v>
+        <v>420</v>
       </c>
       <c r="I4">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="J4">
-        <v>320</v>
+        <v>700</v>
       </c>
       <c r="K4">
         <v>240</v>
@@ -2914,6 +3054,24 @@
       </c>
       <c r="P4" t="s">
         <v>22</v>
+      </c>
+      <c r="Q4">
+        <v>320</v>
+      </c>
+      <c r="R4">
+        <v>220</v>
+      </c>
+      <c r="S4">
+        <v>63</v>
+      </c>
+      <c r="T4">
+        <v>99</v>
+      </c>
+      <c r="U4">
+        <v>42</v>
+      </c>
+      <c r="V4">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/data/Excel/GuLiStrikeSecondaryWeapons.xlsx
+++ b/data/Excel/GuLiStrikeSecondaryWeapons.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="230">
   <si>
     <t>id</t>
   </si>
@@ -671,6 +671,45 @@
   </si>
   <si>
     <t>主动Q导弹；射程与冷却取SecondaryUnitSkills/Skills；保留本槽伤害升级与挂点，自动攻速列不参与Q冷却</t>
+  </si>
+  <si>
+    <t>ProjectileSpreadAngleDegrees</t>
+  </si>
+  <si>
+    <t>ProjectileCount</t>
+  </si>
+  <si>
+    <t>先驱号左右主枪同时发射；每枪1发/秒，每发10伤害，总锥角2度</t>
+  </si>
+  <si>
+    <t>SweeperSummon_Strafe</t>
+  </si>
+  <si>
+    <t>召唤扫荡者原单枪数值</t>
+  </si>
+  <si>
+    <t>Pioneer_AimTarget</t>
+  </si>
+  <si>
+    <t>先驱号真实游戏包围盒中心</t>
+  </si>
+  <si>
+    <t>Pioneer_BasicAttack_Muzzle_0</t>
+  </si>
+  <si>
+    <t>VAT与CPU共享的ShotgunTop_L枪口</t>
+  </si>
+  <si>
+    <t>SweeperSummon_FourFRobot_AimTarget</t>
+  </si>
+  <si>
+    <t>SweeperSummon_FourFRobot_BasicAttack_Muzzle_0</t>
+  </si>
+  <si>
+    <t>Pioneer_BasicAttack_Muzzle_1</t>
+  </si>
+  <si>
+    <t>VAT与CPU共享的ShotgunTop_R枪口</t>
   </si>
 </sst>
 </file>
@@ -1346,6 +1385,12 @@
       <c r="N1" t="s">
         <v>193</v>
       </c>
+      <c r="O1" t="s">
+        <v>217</v>
+      </c>
+      <c r="P1" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
@@ -1390,6 +1435,12 @@
       <c r="N2" t="s">
         <v>35</v>
       </c>
+      <c r="O2" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
@@ -1434,6 +1485,12 @@
       <c r="N3" t="s">
         <v>11</v>
       </c>
+      <c r="O3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -1443,7 +1500,7 @@
         <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>219</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1464,7 +1521,7 @@
         <v>1</v>
       </c>
       <c r="J4">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="K4" t="s">
         <v>189</v>
@@ -1477,6 +1534,12 @@
       </c>
       <c r="N4">
         <v>3</v>
+      </c>
+      <c r="O4">
+        <v>2</v>
+      </c>
+      <c r="P4">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -1508,7 +1571,7 @@
         <v>2</v>
       </c>
       <c r="J5">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="K5" t="s">
         <v>189</v>
@@ -1521,6 +1584,12 @@
       </c>
       <c r="N5">
         <v>3</v>
+      </c>
+      <c r="O5">
+        <v>2</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1557,6 +1626,12 @@
       <c r="K6" t="s">
         <v>189</v>
       </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -1592,6 +1667,12 @@
       <c r="K7" t="s">
         <v>189</v>
       </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -1626,6 +1707,62 @@
       </c>
       <c r="K8" t="s">
         <v>190</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>220</v>
+      </c>
+      <c r="C9" t="s">
+        <v>221</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>2000</v>
+      </c>
+      <c r="K9" t="s">
+        <v>189</v>
+      </c>
+      <c r="L9">
+        <v>2400</v>
+      </c>
+      <c r="M9">
+        <v>5</v>
+      </c>
+      <c r="N9">
+        <v>3</v>
+      </c>
+      <c r="O9">
+        <v>2</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1761,10 +1898,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>222</v>
       </c>
       <c r="C4" t="s">
-        <v>182</v>
+        <v>223</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1782,13 +1919,13 @@
         <v>58</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>24.76776885986328</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>650</v>
+        <v>226.7468723546026</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
@@ -1799,10 +1936,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>224</v>
       </c>
       <c r="C5" t="s">
-        <v>183</v>
+        <v>225</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1820,13 +1957,13 @@
         <v>62</v>
       </c>
       <c r="I5">
-        <v>757.2613716125488</v>
+        <v>279.1171875</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>-143.30313110351562</v>
       </c>
       <c r="K5">
-        <v>588.1241798400879</v>
+        <v>241.1873321533203</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -2019,6 +2156,117 @@
         <v>2335.8587859</v>
       </c>
       <c r="L10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>226</v>
+      </c>
+      <c r="C11" t="s">
+        <v>182</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="F11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>650</v>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I12">
+        <v>757.2613716125488</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>588.1241798400879</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>228</v>
+      </c>
+      <c r="C13" t="s">
+        <v>229</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>203</v>
+      </c>
+      <c r="I13">
+        <v>279.1171875</v>
+      </c>
+      <c r="J13">
+        <v>143.3031463623047</v>
+      </c>
+      <c r="K13">
+        <v>241.1873321533203</v>
+      </c>
+      <c r="L13" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3044,7 +3292,7 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="N4">
         <v>2</v>

--- a/data/Excel/GuLiStrikeSecondaryWeapons.xlsx
+++ b/data/Excel/GuLiStrikeSecondaryWeapons.xlsx
@@ -1527,7 +1527,7 @@
         <v>189</v>
       </c>
       <c r="L4">
-        <v>2400</v>
+        <v>4800</v>
       </c>
       <c r="M4">
         <v>5</v>
@@ -1577,7 +1577,7 @@
         <v>189</v>
       </c>
       <c r="L5">
-        <v>2400</v>
+        <v>4800</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -1750,7 +1750,7 @@
         <v>189</v>
       </c>
       <c r="L9">
-        <v>2400</v>
+        <v>4800</v>
       </c>
       <c r="M9">
         <v>5</v>
